--- a/output/resumen_filtrado.xlsx
+++ b/output/resumen_filtrado.xlsx
@@ -549,12 +549,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -587,12 +587,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -613,12 +613,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-11, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-11, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -651,19 +651,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-14, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-14, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -715,12 +715,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-10, 2026-03-11, 2026-03-18, 2026-03-31</t>
+          <t>2026-03-06, 2026-03-10, 2026-03-11, 2026-03-20, 2026-03-31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-18</t>
+          <t>2026-03-06, 2026-03-11, 2026-03-20</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -741,19 +741,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-20, 2026-03-31</t>
+          <t>2026-03-09, 2026-03-11, 2026-03-20, 2026-03-31</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-20</t>
+          <t>2026-03-11, 2026-03-20</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -779,19 +779,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+          <t>2026-03-06, 2026-03-14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+          <t>2026-03-06, 2026-03-14</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-18</t>
+          <t>2026-03-09, 2026-03-18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-18, 2026-03-21</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-18, 2026-03-21</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-21, 2026-03-30</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-21</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-27</t>
+          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-27</t>
+          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -1163,19 +1163,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1189,19 +1189,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-06, 2026-03-20, 2026-03-30</t>
+          <t>2026-03-03, 2026-03-11, 2026-03-20, 2026-03-30</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-20</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="13">

--- a/output/resumen_filtrado.xlsx
+++ b/output/resumen_filtrado.xlsx
@@ -552,16 +552,12 @@
           <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -656,14 +652,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-14, 2026-03-20</t>
+          <t>2026-03-06, 2026-03-20</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -720,14 +716,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -746,14 +742,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-11, 2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
@@ -784,14 +780,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-14</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -910,16 +906,12 @@
           <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1002,14 +994,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-14, 2026-03-21</t>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
